--- a/Budget/data/budget_2024.xlsx
+++ b/Budget/data/budget_2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\NLP\anambra\Budget\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94D525F0-AFCB-4002-A0CE-53917E67534A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CC295C-F630-44B6-9642-B84F41817D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{283BA25A-3651-4F30-BDFC-5DC6F96FEF44}"/>
   </bookViews>
@@ -520,7 +520,7 @@
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/Budget/data/budget_2024.xlsx
+++ b/Budget/data/budget_2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\NLP\anambra\Budget\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CC295C-F630-44B6-9642-B84F41817D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FDA167-BE94-4A75-8ADE-8B551AE8502F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{283BA25A-3651-4F30-BDFC-5DC6F96FEF44}"/>
   </bookViews>
@@ -87,24 +87,12 @@
     <t>Judicial Service Commission</t>
   </si>
   <si>
-    <t>Anambra State Internal Revenue Service</t>
-  </si>
-  <si>
     <t>Ministry of Information</t>
   </si>
   <si>
     <t>Office of the Head of Service</t>
   </si>
   <si>
-    <t>Anambra State Investment Promotion &amp; Protection Agency</t>
-  </si>
-  <si>
-    <t>Christian Pilgrims Welfare Board</t>
-  </si>
-  <si>
-    <t>Muslim Pilgrims Welfare Board</t>
-  </si>
-  <si>
     <t>Ministry of Homeland Affairs</t>
   </si>
   <si>
@@ -136,12 +124,27 @@
   </si>
   <si>
     <t>Ministry of Lands</t>
+  </si>
+  <si>
+    <t>Office of the Auditor General</t>
+  </si>
+  <si>
+    <t>Civil Service Commision</t>
+  </si>
+  <si>
+    <t>Local Government Civil Service Commision</t>
+  </si>
+  <si>
+    <t>Awka Capital Terrirtory Development Authority</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;₦&quot;#,##0.00;[Red]\-&quot;₦&quot;#,##0.00"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -151,9 +154,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -192,15 +195,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -520,10 +520,10 @@
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="36" customWidth="1"/>
+    <col min="1" max="6" width="82.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -539,628 +539,628 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3">
-        <v>6535541004</v>
-      </c>
-      <c r="C2" s="3">
-        <v>30607825825</v>
-      </c>
-      <c r="D2" s="3">
-        <v>37143366813</v>
-      </c>
-      <c r="E2" s="3">
-        <v>9580000000</v>
-      </c>
-      <c r="F2" s="3">
-        <v>46723366813</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="2">
+        <v>4785592518.9499998</v>
+      </c>
+      <c r="C2" s="2">
+        <v>23488240368.040001</v>
+      </c>
+      <c r="D2" s="2">
+        <v>28273832886.98</v>
+      </c>
+      <c r="E2" s="2">
+        <v>7136936515.1099997</v>
+      </c>
+      <c r="F2" s="2">
+        <v>35410769402.089996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3">
-        <v>451446616.60000002</v>
-      </c>
-      <c r="C3" s="3">
-        <v>661054701</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1112501318</v>
-      </c>
-      <c r="E3" s="3">
-        <v>2746000000</v>
-      </c>
-      <c r="F3" s="3">
-        <v>3858501318</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="2">
+        <v>351345225.61000001</v>
+      </c>
+      <c r="C3" s="2">
+        <v>857410713.76999998</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1208755939.3800001</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1962500000</v>
+      </c>
+      <c r="F3" s="2">
+        <v>3171255939.3800001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3">
-        <v>359861189.19999999</v>
-      </c>
-      <c r="C4" s="3">
-        <v>26812946.48</v>
-      </c>
-      <c r="D4" s="3">
-        <v>386674135.69999999</v>
-      </c>
-      <c r="E4" s="3">
-        <v>6225500000</v>
-      </c>
-      <c r="F4" s="3">
-        <v>6615174136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>17223828729.939999</v>
+      </c>
+      <c r="C4" s="2">
+        <v>15235131244.969999</v>
+      </c>
+      <c r="D4" s="2">
+        <v>32458959974.91</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3093100000</v>
+      </c>
+      <c r="F4" s="2">
+        <v>35552059974.910004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3">
-        <v>209899318.19999999</v>
-      </c>
-      <c r="C5" s="3">
-        <v>34427354.549999997</v>
-      </c>
-      <c r="D5" s="3">
-        <v>250326672.80000001</v>
-      </c>
-      <c r="E5" s="3">
-        <v>269320000000</v>
-      </c>
-      <c r="F5" s="3">
-        <v>271850848673</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>159887041</v>
+      </c>
+      <c r="C5" s="2">
+        <v>48790941.82</v>
+      </c>
+      <c r="D5" s="2">
+        <v>208677982.81999999</v>
+      </c>
+      <c r="E5" s="2">
+        <v>190711200000</v>
+      </c>
+      <c r="F5" s="2">
+        <v>190919877982.82001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3">
-        <v>279336206.80000001</v>
-      </c>
-      <c r="C6" s="3">
-        <v>98971382.079999998</v>
-      </c>
-      <c r="D6" s="3">
-        <v>283088351.69999999</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>283088351.69999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>93170332</v>
+      </c>
+      <c r="C6" s="2">
+        <v>224691342</v>
+      </c>
+      <c r="D6" s="2">
+        <v>317861674</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2064712352</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2382574026</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3">
-        <v>613367392.20000005</v>
-      </c>
-      <c r="C7" s="3">
-        <v>20339716.079999998</v>
-      </c>
-      <c r="D7" s="3">
-        <v>632057108.29999995</v>
-      </c>
-      <c r="E7" s="3">
-        <v>3125000000</v>
-      </c>
-      <c r="F7" s="3">
-        <v>3758707108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>447745602</v>
+      </c>
+      <c r="C7" s="2">
+        <v>18490650.98</v>
+      </c>
+      <c r="D7" s="2">
+        <v>466236252.98000002</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1923000000</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2389236252.98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3">
-        <v>120066559.5</v>
-      </c>
-      <c r="C8" s="3">
-        <v>13384103.65</v>
-      </c>
-      <c r="D8" s="3">
-        <v>133450663.09999999</v>
-      </c>
-      <c r="E8" s="3">
-        <v>10411000000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>10544450663</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>88588784.200000003</v>
+      </c>
+      <c r="C8" s="2">
+        <v>12167366.949999999</v>
+      </c>
+      <c r="D8" s="2">
+        <v>100756151.15000001</v>
+      </c>
+      <c r="E8" s="2">
+        <v>10540996000</v>
+      </c>
+      <c r="F8" s="2">
+        <v>10641752151.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3">
-        <v>109311864</v>
-      </c>
-      <c r="C9" s="3">
-        <v>14984967.33</v>
-      </c>
-      <c r="D9" s="3">
-        <v>127296831.3</v>
-      </c>
-      <c r="E9" s="3">
-        <v>399000000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>526296831.30000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>80222760</v>
+      </c>
+      <c r="C9" s="2">
+        <v>13622697.58</v>
+      </c>
+      <c r="D9" s="2">
+        <v>93845457.579999998</v>
+      </c>
+      <c r="E9" s="2">
+        <v>654478000</v>
+      </c>
+      <c r="F9" s="2">
+        <v>748323457.58000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3">
-        <v>697308192.60000002</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3">
-        <v>697308192.60000002</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <v>697308192.60000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>33292190</v>
+      </c>
+      <c r="C10" s="2">
+        <v>12600000</v>
+      </c>
+      <c r="D10" s="2">
+        <v>45892190</v>
+      </c>
+      <c r="E10" s="2">
+        <v>312570000</v>
+      </c>
+      <c r="F10" s="2">
+        <v>358462190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3">
-        <v>508275684.10000002</v>
-      </c>
-      <c r="C11" s="3">
-        <v>18705378.600000001</v>
-      </c>
-      <c r="D11" s="3">
-        <v>433892105.19999999</v>
-      </c>
-      <c r="E11" s="3">
-        <v>14246833333</v>
-      </c>
-      <c r="F11" s="3">
-        <v>18685743337</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>395711583</v>
+      </c>
+      <c r="C11" s="2">
+        <v>49020358.310000002</v>
+      </c>
+      <c r="D11" s="2">
+        <v>444731941.31</v>
+      </c>
+      <c r="E11" s="2">
+        <v>10210000000</v>
+      </c>
+      <c r="F11" s="2">
+        <v>10654731941.309999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3">
-        <v>22572200</v>
-      </c>
-      <c r="C12" s="3">
-        <v>19227600</v>
-      </c>
-      <c r="D12" s="3">
-        <v>41799800</v>
-      </c>
-      <c r="E12" s="3">
-        <v>935000000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>976799800</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>16123000</v>
+      </c>
+      <c r="C12" s="2">
+        <v>13734000</v>
+      </c>
+      <c r="D12" s="2">
+        <v>29857000</v>
+      </c>
+      <c r="E12" s="2">
+        <v>445000000</v>
+      </c>
+      <c r="F12" s="2">
+        <v>474857000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="3">
-        <v>1559128693</v>
-      </c>
-      <c r="C13" s="3">
-        <v>3245100261</v>
-      </c>
-      <c r="D13" s="3">
-        <v>4804228954</v>
-      </c>
-      <c r="E13" s="3">
-        <v>6058000000</v>
-      </c>
-      <c r="F13" s="3">
-        <v>10862228954</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>1126208467.5999999</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2704250217.4000001</v>
+      </c>
+      <c r="D13" s="2">
+        <v>3830458685</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3404870000</v>
+      </c>
+      <c r="F13" s="2">
+        <v>7235328685</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="3">
-        <v>70113487.5</v>
-      </c>
-      <c r="C14" s="3">
-        <v>19910052.690000001</v>
-      </c>
-      <c r="D14" s="3">
-        <v>90023540.189999998</v>
-      </c>
-      <c r="E14" s="3">
-        <v>185000000</v>
-      </c>
-      <c r="F14" s="3">
-        <v>275023540.19999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>50081062.5</v>
+      </c>
+      <c r="C14" s="2">
+        <v>18100047.899999999</v>
+      </c>
+      <c r="D14" s="2">
+        <v>68181110.400000006</v>
+      </c>
+      <c r="E14" s="2">
+        <v>129120000</v>
+      </c>
+      <c r="F14" s="2">
+        <v>197301110.40000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="3">
-        <v>5983750263</v>
-      </c>
-      <c r="C15" s="3">
-        <v>91849237.680000007</v>
-      </c>
-      <c r="D15" s="3">
-        <v>6072263617</v>
-      </c>
-      <c r="E15" s="3">
-        <v>7985600000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>14057863617</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>4276032513.6700001</v>
+      </c>
+      <c r="C15" s="2">
+        <v>190303186.77000001</v>
+      </c>
+      <c r="D15" s="2">
+        <v>4466335700.4399996</v>
+      </c>
+      <c r="E15" s="2">
+        <v>4938824000</v>
+      </c>
+      <c r="F15" s="2">
+        <v>9405159700.4400005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="3">
-        <v>565015287.39999998</v>
-      </c>
-      <c r="C16" s="3">
-        <v>109712371.7</v>
-      </c>
-      <c r="D16" s="3">
-        <v>674727659.10000002</v>
-      </c>
-      <c r="E16" s="3">
-        <v>699000000</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1373727659</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <v>251777755</v>
+      </c>
+      <c r="C16" s="2">
+        <v>584736800.97000003</v>
+      </c>
+      <c r="D16" s="2">
+        <v>836514555.97000003</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1879318076</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2715832631.9699998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="3">
-        <v>293066530.19999999</v>
-      </c>
-      <c r="C17" s="3">
-        <v>19211374</v>
-      </c>
-      <c r="D17" s="3">
-        <v>312277904.19999999</v>
-      </c>
-      <c r="E17" s="3">
-        <v>5443118000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>5755395904</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <v>772664723</v>
+      </c>
+      <c r="C17" s="2">
+        <v>211371944.34999999</v>
+      </c>
+      <c r="D17" s="2">
+        <v>984036667.35000002</v>
+      </c>
+      <c r="E17" s="2">
+        <v>885906028</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1869942695.3499999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="3">
-        <v>1066410186</v>
-      </c>
-      <c r="C18" s="3">
-        <v>295920722.10000002</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1362330908</v>
-      </c>
-      <c r="E18" s="3">
-        <v>866000000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>2228330908</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <v>98414280.75</v>
+      </c>
+      <c r="C18" s="2">
+        <v>13734000</v>
+      </c>
+      <c r="D18" s="2">
+        <v>112148280.75</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1262180000</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1374328280.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="3">
-        <v>221583990</v>
-      </c>
-      <c r="C19" s="3">
-        <v>0</v>
-      </c>
-      <c r="D19" s="3">
-        <v>221583990</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>221583990</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="2">
+        <v>84454068</v>
+      </c>
+      <c r="C19" s="2">
+        <v>15320080</v>
+      </c>
+      <c r="D19" s="2">
+        <v>99774148</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2271000000</v>
+      </c>
+      <c r="F19" s="2">
+        <v>2370774148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="3">
-        <v>7276500</v>
-      </c>
-      <c r="C20" s="3">
-        <v>0</v>
-      </c>
-      <c r="D20" s="3">
-        <v>7276500</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>7276500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <v>101665577.8</v>
+      </c>
+      <c r="C20" s="2">
+        <v>29434000</v>
+      </c>
+      <c r="D20" s="2">
+        <v>131099577.8</v>
+      </c>
+      <c r="E20" s="2">
+        <v>10525000000</v>
+      </c>
+      <c r="F20" s="2">
+        <v>10656099577.799999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="3">
-        <v>7210350</v>
-      </c>
-      <c r="C21" s="3">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3">
-        <v>7210350</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <v>7210350</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="2">
+        <v>203764527</v>
+      </c>
+      <c r="C21" s="2">
+        <v>26554500.010000002</v>
+      </c>
+      <c r="D21" s="2">
+        <v>230319027.00999999</v>
+      </c>
+      <c r="E21" s="2">
+        <v>627000000</v>
+      </c>
+      <c r="F21" s="2">
+        <v>857319027.00999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="3">
-        <v>135779993.09999999</v>
-      </c>
-      <c r="C22" s="3">
-        <v>15107400</v>
-      </c>
-      <c r="D22" s="3">
-        <v>150887393.09999999</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2701500000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2852387393</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>188158070</v>
+      </c>
+      <c r="C22" s="2">
+        <v>23815357.16</v>
+      </c>
+      <c r="D22" s="2">
+        <v>211973427.16</v>
+      </c>
+      <c r="E22" s="2">
+        <v>3180000000</v>
+      </c>
+      <c r="F22" s="2">
+        <v>3391973427.1599998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="3">
-        <v>114446652.8</v>
-      </c>
-      <c r="C23" s="3">
-        <v>9751322</v>
-      </c>
-      <c r="D23" s="3">
-        <v>124197974.8</v>
-      </c>
-      <c r="E23" s="3">
-        <v>2610600000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>2962226775</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="2">
+        <v>412025217</v>
+      </c>
+      <c r="C23" s="2">
+        <v>39182632</v>
+      </c>
+      <c r="D23" s="2">
+        <v>451207849</v>
+      </c>
+      <c r="E23" s="2">
+        <v>5589790000</v>
+      </c>
+      <c r="F23" s="2">
+        <v>6040997849</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="3">
-        <v>138600177.30000001</v>
-      </c>
-      <c r="C24" s="3">
-        <v>13860000</v>
-      </c>
-      <c r="D24" s="3">
-        <v>152460177.30000001</v>
-      </c>
-      <c r="E24" s="3">
-        <v>10375000000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>10599650177</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <v>454139139.87</v>
+      </c>
+      <c r="C24" s="2">
+        <v>66698115.93</v>
+      </c>
+      <c r="D24" s="2">
+        <v>520837255.80000001</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2725050000</v>
+      </c>
+      <c r="F24" s="2">
+        <v>3245887255.8000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="3">
-        <v>280883462.60000002</v>
-      </c>
-      <c r="C25" s="3">
-        <v>21656250</v>
-      </c>
-      <c r="D25" s="3">
-        <v>302539712.60000002</v>
-      </c>
-      <c r="E25" s="3">
-        <v>547000000</v>
-      </c>
-      <c r="F25" s="3">
-        <v>857093412.60000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="2">
+        <v>10032003614</v>
+      </c>
+      <c r="C25" s="2">
+        <v>361235884.00999999</v>
+      </c>
+      <c r="D25" s="2">
+        <v>10393239498.01</v>
+      </c>
+      <c r="E25" s="2">
+        <v>18209210000</v>
+      </c>
+      <c r="F25" s="2">
+        <v>28602449498.009998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="3">
-        <v>198035997.80000001</v>
-      </c>
-      <c r="C26" s="3">
-        <v>61476821.460000001</v>
-      </c>
-      <c r="D26" s="3">
-        <v>259512819.30000001</v>
-      </c>
-      <c r="E26" s="3">
-        <v>3611000000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>620612819.29999995</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="2">
+        <v>111991335</v>
+      </c>
+      <c r="C26" s="2">
+        <v>86230126.5</v>
+      </c>
+      <c r="D26" s="2">
+        <v>86230126.5</v>
+      </c>
+      <c r="E26" s="2">
+        <v>3404000000</v>
+      </c>
+      <c r="F26" s="2">
+        <v>509954241.30000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="3">
-        <v>261024782.19999999</v>
-      </c>
-      <c r="C27" s="3">
-        <v>13860000</v>
-      </c>
-      <c r="D27" s="3">
-        <v>274884782.19999999</v>
-      </c>
-      <c r="E27" s="3">
-        <v>3479700000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>3754814782</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="2">
+        <v>3271824560</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2337982075.4400001</v>
+      </c>
+      <c r="D27" s="2">
+        <v>5609806635.4399996</v>
+      </c>
+      <c r="E27" s="2">
+        <v>16822033554</v>
+      </c>
+      <c r="F27" s="2">
+        <v>22431840189.439999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="3">
-        <v>628826114.29999995</v>
-      </c>
-      <c r="C28" s="3">
-        <v>71476821.459999993</v>
-      </c>
-      <c r="D28" s="3">
-        <v>646970954.29999995</v>
-      </c>
-      <c r="E28" s="3">
-        <v>2876000000</v>
-      </c>
-      <c r="F28" s="3">
-        <v>934570954.29999995</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="2">
+        <v>735149579</v>
+      </c>
+      <c r="C28" s="2">
+        <v>212568147.99000001</v>
+      </c>
+      <c r="D28" s="2">
+        <v>947717726.99000001</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2048699401</v>
+      </c>
+      <c r="F28" s="2">
+        <v>2996417127.9899998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="3">
-        <v>332935929.10000002</v>
-      </c>
-      <c r="C29" s="3">
-        <v>837764026.20000005</v>
-      </c>
-      <c r="D29" s="3">
-        <v>1170699955</v>
-      </c>
-      <c r="E29" s="3">
-        <v>38374500000</v>
-      </c>
-      <c r="F29" s="3">
-        <v>50181499955</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="2">
+        <v>221223111</v>
+      </c>
+      <c r="C29" s="2">
+        <v>13151650</v>
+      </c>
+      <c r="D29" s="2">
+        <v>234374761</v>
+      </c>
+      <c r="E29" s="2">
+        <v>152280000</v>
+      </c>
+      <c r="F29" s="2">
+        <v>386654761</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="3">
-        <v>151732064.19999999</v>
-      </c>
-      <c r="C30" s="3">
-        <v>17822177.100000001</v>
-      </c>
-      <c r="D30" s="3">
-        <v>169554241.30000001</v>
-      </c>
-      <c r="E30" s="3">
-        <v>3404000000</v>
-      </c>
-      <c r="F30" s="3">
-        <v>509954241.30000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
+        <v>68775809</v>
+      </c>
+      <c r="C30" s="2">
+        <v>17327165</v>
+      </c>
+      <c r="D30" s="2">
+        <v>86102974</v>
+      </c>
+      <c r="E30" s="2">
+        <v>30000000</v>
+      </c>
+      <c r="F30" s="2">
+        <v>116102974</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="3">
-        <v>538449487.79999995</v>
-      </c>
-      <c r="C31" s="3">
+      <c r="B31" s="2">
+        <v>31264238</v>
+      </c>
+      <c r="C31" s="2">
         <v>0</v>
       </c>
-      <c r="D31" s="3">
-        <v>538449487.79999995</v>
-      </c>
-      <c r="E31" s="3">
+      <c r="D31" s="2">
+        <v>31264238</v>
+      </c>
+      <c r="E31" s="2">
         <v>0</v>
       </c>
-      <c r="F31" s="3">
-        <v>538449487.79999995</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F31" s="2">
+        <v>31264238</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="3">
-        <v>278238168.19999999</v>
-      </c>
-      <c r="C32" s="3">
-        <v>20182554</v>
-      </c>
-      <c r="D32" s="3">
-        <v>298420722.19999999</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1749000000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>473320722.19999999</v>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>154618900.00999999</v>
+      </c>
+      <c r="D32" s="2">
+        <v>154618900.00999999</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <v>154618900.00999999</v>
       </c>
     </row>
   </sheetData>
